--- a/etf_holdings/2026-09-02_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-09-02_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH13"/>
+  <dimension ref="A1:CZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,172 +439,522 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>00981A_異動類型</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>00981A_調整方向</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>00981A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>00981A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>00981A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>00981A_權重_今日</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>00981A_權重變化</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>00981A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>00981A_股數_今日</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>00981A_股數變化</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>00991A_異動類型</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>00991A_調整方向</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>00991A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>00991A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>00991A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>00991A_權重_今日</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>00991A_權重變化</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>00991A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>00991A_股數_今日</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>00991A_股數變化</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>00982A_異動類型</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>00982A_調整方向</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>00982A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>00982A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>00982A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>00982A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>00982A_權重變化</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>00982A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>00982A_股數_今日</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>00982A_股數變化</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>00403A_異動類型</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>00403A_調整方向</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>00403A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>00403A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>00403A_權重變化</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>00403A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>00403A_股數_今日</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>00403A_股數變化</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
           <t>00985A_異動類型</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>00985A_調整方向</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>00985A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>00985A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>00985A_權重_昨日</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>00985A_權重_今日</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>00985A_權重變化</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>00985A_股數_昨日</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>00985A_股數_今日</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>00985A_股數變化</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>00992A_異動類型</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>00992A_調整方向</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>00992A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>00992A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>00992A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>00992A_權重_今日</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>00992A_權重變化</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>00992A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>00992A_股數_今日</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>00992A_股數變化</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>00405A_異動類型</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>00405A_調整方向</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>00405A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>00405A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>00405A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>00405A_權重_今日</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>00405A_權重變化</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>00405A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>00405A_股數_今日</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>00405A_股數變化</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
         <is>
           <t>00407A_異動類型</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>00407A_調整方向</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>00407A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>00407A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>00407A_權重_昨日</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>00407A_權重_今日</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>00407A_權重變化</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>00407A_股數_昨日</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>00407A_股數_今日</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>00407A_股數變化</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>00993A_異動類型</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>00993A_調整方向</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>00993A_權重_昨日</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>00993A_權重_今日</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>00993A_權重變化</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>00993A_股數_昨日</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>00993A_股數_今日</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>00993A_股數變化</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>00400A_異動類型</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>00400A_調整方向</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>00400A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>00400A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>00400A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>00400A_權重_今日</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>00400A_權重變化</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>00400A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>00400A_股數_今日</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>00400A_股數變化</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00400A,00403A,00405A,00981A,00982A,00985A,00991A,00992A,00993A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,50 +969,86 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>5.83%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>171000</v>
+        <v>2176000</v>
       </c>
       <c r="M2" t="n">
-        <v>804000</v>
+        <v>6490561</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>633,000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+          <t>4,314,561</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>緯穎科技</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>緯穎科技</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>5.46%</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>5.60%</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>580000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1730020</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1,150,020</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>持續持有</t>
@@ -670,63 +1056,349 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>7.51%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>7.02%</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>-0.49%</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>510000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1391225</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>881,225</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>3.29%</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>3.39%</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>700000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>2087956</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>1,387,956</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>緯穎科技服務</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>緯穎科技服務</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>3.61%</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>4.11%</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>+0.50%</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>53000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>56000</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>1.38%</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>1.40%</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="BJ2" t="n">
+        <v>77000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>229675</v>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>152,675</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>1.34%</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>1.39%</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="BT2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>149139</v>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>99,139</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1.80%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>1.69%</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>-0.11%</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1435000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1338000</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-97,000</t>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>3.79%</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>3.49%</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
+        </is>
+      </c>
+      <c r="CN2" t="n">
+        <v>55000</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>47000</v>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>5.86%</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>5.97%</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="CX2" t="n">
+        <v>221000</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>659197</v>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>438,197</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>致茂電子</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00981A,00982A,00985A,00993A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -736,43 +1408,43 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>致茂電子</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>致茂電子</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>9.21%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>9.17%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5000</v>
+        <v>4757000</v>
       </c>
       <c r="M3" t="n">
-        <v>43000</v>
+        <v>4750000</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>38,000</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -797,58 +1469,200 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>22000</v>
+        <v>317000</v>
       </c>
       <c r="AG3" t="n">
-        <v>11000</v>
+        <v>315000</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-11,000</t>
-        </is>
-      </c>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>台光電子材料</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>台光電子材料</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>2.48%</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2.76%</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>+0.28%</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>47000</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>52000</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
+      <c r="CD3" t="inlineStr"/>
+      <c r="CE3" t="inlineStr"/>
+      <c r="CF3" t="inlineStr"/>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>6.07%</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>5.68%</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>-0.39%</t>
+        </is>
+      </c>
+      <c r="CN3" t="n">
+        <v>114000</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>106000</v>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr"/>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="inlineStr"/>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
+      <c r="CX3" t="inlineStr"/>
+      <c r="CY3" t="inlineStr"/>
+      <c r="CZ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00403A,00981A,00982A,00993A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -858,43 +1672,43 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>3.91%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>3.51%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47000</v>
+        <v>18679000</v>
       </c>
       <c r="M4" t="n">
-        <v>52000</v>
+        <v>16811000</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>-1,868,000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -919,106 +1733,212 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>6.07%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="AF4" t="n">
-        <v>114000</v>
+        <v>950000</v>
       </c>
       <c r="AG4" t="n">
-        <v>106000</v>
+        <v>942000</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>-8,000</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>2.20%</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>1.65%</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>-0.55%</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-1,500,000</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>1.13%</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>-0.55%</t>
+        </is>
+      </c>
+      <c r="CN4" t="n">
+        <v>200000</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr"/>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr"/>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.95%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2.10%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>+1.15%</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>146000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>313000</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>167,000</t>
-        </is>
-      </c>
+          <t>00403A,00982A,00993A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -1041,58 +1961,182 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="AF5" t="n">
-        <v>59000</v>
+        <v>3273000</v>
       </c>
       <c r="AG5" t="n">
-        <v>29000</v>
+        <v>3258000</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-30,000</t>
-        </is>
-      </c>
+          <t>-15,000</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.06%</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>300000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr"/>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="inlineStr"/>
+      <c r="CE5" t="inlineStr"/>
+      <c r="CF5" t="inlineStr"/>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>光寶科技</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>光寶科技</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="CN5" t="n">
+        <v>175000</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>87000</v>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>-88,000</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr"/>
+      <c r="CR5" t="inlineStr"/>
+      <c r="CS5" t="inlineStr"/>
+      <c r="CT5" t="inlineStr"/>
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="inlineStr"/>
+      <c r="CX5" t="inlineStr"/>
+      <c r="CY5" t="inlineStr"/>
+      <c r="CZ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00407A,00993A</t>
+          <t>00982A,00985A,00993A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -1105,268 +2149,462 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>2.12%</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>1.16%</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>-0.96%</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>1025000</v>
-      </c>
-      <c r="W6" t="n">
-        <v>595000</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-430,000</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>5243000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>5205000</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>-38,000</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>聯華電子</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>聯華電子</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>+0.79%</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>171000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>804000</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>633,000</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr"/>
+      <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="inlineStr"/>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>4.10%</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>3.76%</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>-0.34%</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>778000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>763000</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>-15,000</t>
-        </is>
-      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="CN6" t="n">
+        <v>1435000</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>1338000</v>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>-97,000</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr"/>
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="inlineStr"/>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr"/>
+      <c r="CW6" t="inlineStr"/>
+      <c r="CX6" t="inlineStr"/>
+      <c r="CY6" t="inlineStr"/>
+      <c r="CZ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+          <t>00982A,00991A,00993A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>文曄科技</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>文曄科技</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.89%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.05%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-0.84%</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>475000</v>
-      </c>
-      <c r="M7" t="n">
-        <v>27000</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-448,000</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>智邦科技</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>智邦科技</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4.26%</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-150,000</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr"/>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>文曄</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2.61%</t>
+        </is>
+      </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.28%</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
+          <t>2.57%</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>627000</v>
+      </c>
       <c r="AG7" t="n">
-        <v>149000</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>621000</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>-6,000</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr"/>
+      <c r="CE7" t="inlineStr"/>
+      <c r="CF7" t="inlineStr"/>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>2.98%</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>2.94%</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="CN7" t="n">
+        <v>151000</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>140000</v>
+      </c>
+      <c r="CP7" t="inlineStr">
+        <is>
+          <t>-11,000</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr"/>
+      <c r="CR7" t="inlineStr"/>
+      <c r="CS7" t="inlineStr"/>
+      <c r="CT7" t="inlineStr"/>
+      <c r="CU7" t="inlineStr"/>
+      <c r="CV7" t="inlineStr"/>
+      <c r="CW7" t="inlineStr"/>
+      <c r="CX7" t="inlineStr"/>
+      <c r="CY7" t="inlineStr"/>
+      <c r="CZ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>欣興電子</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>欣興電子</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>欣興電子</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1.94%</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2.30%</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>+0.36%</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>202000</v>
-      </c>
-      <c r="M8" t="n">
-        <v>252000</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>50,000</t>
-        </is>
-      </c>
+          <t>00982A,00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -1389,106 +2627,212 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>5.46%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4.19%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="AF8" t="n">
-        <v>563000</v>
+        <v>837000</v>
       </c>
       <c r="AG8" t="n">
-        <v>454000</v>
+        <v>830000</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-109,000</t>
-        </is>
-      </c>
+          <t>-7,000</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>致茂電子</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>致茂電子</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.09%</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.82%</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>+0.73%</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>43000</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>38,000</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr"/>
+      <c r="CE8" t="inlineStr"/>
+      <c r="CF8" t="inlineStr"/>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="CN8" t="n">
+        <v>22000</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>11000</v>
+      </c>
+      <c r="CP8" t="inlineStr">
+        <is>
+          <t>-11,000</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr"/>
+      <c r="CR8" t="inlineStr"/>
+      <c r="CS8" t="inlineStr"/>
+      <c r="CT8" t="inlineStr"/>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr"/>
+      <c r="CW8" t="inlineStr"/>
+      <c r="CX8" t="inlineStr"/>
+      <c r="CY8" t="inlineStr"/>
+      <c r="CZ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>貿聯控股（BizLink Holding In</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>貿聯控股（BizLink Holding In</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>貿聯控股（BizLink Holding In</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1.98%</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2.29%</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>+0.31%</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>95000</v>
-      </c>
-      <c r="M9" t="n">
-        <v>105000</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
+          <t>00982A,00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -1506,63 +2850,205 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>1473000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1466000</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>-7,000</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1.85%</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>1.98%</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>+0.13%</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>88000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>90000</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>2.10%</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>+1.15%</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>146000</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>313000</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>167,000</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="CN9" t="n">
+        <v>59000</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>29000</v>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>-30,000</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr"/>
+      <c r="CR9" t="inlineStr"/>
+      <c r="CS9" t="inlineStr"/>
+      <c r="CT9" t="inlineStr"/>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr"/>
+      <c r="CW9" t="inlineStr"/>
+      <c r="CX9" t="inlineStr"/>
+      <c r="CY9" t="inlineStr"/>
+      <c r="CZ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00407A,00993A</t>
+          <t>00982A,00992A,00993A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -1575,32 +3061,14 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.19%</t>
-        </is>
-      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="n">
-        <v>8000</v>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
@@ -1615,106 +3083,194 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>3.83%</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>39000</v>
+        <v>255000</v>
       </c>
       <c r="AG10" t="n">
-        <v>34000</v>
+        <v>254000</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5,000</t>
-        </is>
-      </c>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>5.96%</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>5.35%</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>-0.61%</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>343000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>293000</v>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>-50,000</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr"/>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr"/>
+      <c r="CE10" t="inlineStr"/>
+      <c r="CF10" t="inlineStr"/>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr"/>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="CK10" t="inlineStr"/>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr"/>
+      <c r="CN10" t="inlineStr"/>
+      <c r="CO10" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CP10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr"/>
+      <c r="CR10" t="inlineStr"/>
+      <c r="CS10" t="inlineStr"/>
+      <c r="CT10" t="inlineStr"/>
+      <c r="CU10" t="inlineStr"/>
+      <c r="CV10" t="inlineStr"/>
+      <c r="CW10" t="inlineStr"/>
+      <c r="CX10" t="inlineStr"/>
+      <c r="CY10" t="inlineStr"/>
+      <c r="CZ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>緯穎科技服務</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>緯穎科技服務</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>緯穎科技服務</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3.61%</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>4.11%</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>+0.50%</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>53000</v>
-      </c>
-      <c r="M11" t="n">
-        <v>56000</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
+          <t>00405A,00982A,00993A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
@@ -1737,284 +3293,5018 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>55000</v>
+        <v>376000</v>
       </c>
       <c r="AG11" t="n">
-        <v>47000</v>
+        <v>374000</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-8,000</t>
-        </is>
-      </c>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>7.71%</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>6.58%</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>-1.13%</t>
+        </is>
+      </c>
+      <c r="BT11" t="n">
+        <v>658000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>558000</v>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
+      <c r="CA11" t="inlineStr"/>
+      <c r="CB11" t="inlineStr"/>
+      <c r="CC11" t="inlineStr"/>
+      <c r="CD11" t="inlineStr"/>
+      <c r="CE11" t="inlineStr"/>
+      <c r="CF11" t="inlineStr"/>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>5.26%</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>4.34%</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>-0.92%</t>
+        </is>
+      </c>
+      <c r="CN11" t="n">
+        <v>158000</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>134000</v>
+      </c>
+      <c r="CP11" t="inlineStr">
+        <is>
+          <t>-24,000</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr"/>
+      <c r="CR11" t="inlineStr"/>
+      <c r="CS11" t="inlineStr"/>
+      <c r="CT11" t="inlineStr"/>
+      <c r="CU11" t="inlineStr"/>
+      <c r="CV11" t="inlineStr"/>
+      <c r="CW11" t="inlineStr"/>
+      <c r="CX11" t="inlineStr"/>
+      <c r="CY11" t="inlineStr"/>
+      <c r="CZ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>鴻勁精密</t>
+          <t>信驊科技</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+          <t>00403A,00991A,00993A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2.49%</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>3.09%</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>+0.60%</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>120500</v>
+      </c>
+      <c r="W12" t="n">
+        <v>140500</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>1.54%</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>2.09%</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>+0.55%</t>
+        </is>
+      </c>
+      <c r="AP12" t="n">
+        <v>149500</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>189500</v>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
+      <c r="BQ12" t="inlineStr"/>
+      <c r="BR12" t="inlineStr"/>
+      <c r="BS12" t="inlineStr"/>
+      <c r="BT12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="inlineStr"/>
+      <c r="BW12" t="inlineStr"/>
+      <c r="BX12" t="inlineStr"/>
+      <c r="BY12" t="inlineStr"/>
+      <c r="BZ12" t="inlineStr"/>
+      <c r="CA12" t="inlineStr"/>
+      <c r="CB12" t="inlineStr"/>
+      <c r="CC12" t="inlineStr"/>
+      <c r="CD12" t="inlineStr"/>
+      <c r="CE12" t="inlineStr"/>
+      <c r="CF12" t="inlineStr"/>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>鴻勁精密</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>鴻勁精密</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1.74%</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0.99%</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>-0.75%</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>31000</v>
-      </c>
-      <c r="M12" t="n">
-        <v>18000</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-13,000</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>鴻勁</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>鴻勁</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1.48%</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>0.73%</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>-0.75%</t>
-        </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>26000</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>13000</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-13,000</t>
-        </is>
-      </c>
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="CJ12" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="CK12" t="inlineStr">
+        <is>
+          <t>3.99%</t>
+        </is>
+      </c>
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>3.35%</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>-0.64%</t>
+        </is>
+      </c>
+      <c r="CN12" t="n">
+        <v>25600</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>20600</v>
+      </c>
+      <c r="CP12" t="inlineStr">
+        <is>
+          <t>-5,000</t>
+        </is>
+      </c>
+      <c r="CQ12" t="inlineStr"/>
+      <c r="CR12" t="inlineStr"/>
+      <c r="CS12" t="inlineStr"/>
+      <c r="CT12" t="inlineStr"/>
+      <c r="CU12" t="inlineStr"/>
+      <c r="CV12" t="inlineStr"/>
+      <c r="CW12" t="inlineStr"/>
+      <c r="CX12" t="inlineStr"/>
+      <c r="CY12" t="inlineStr"/>
+      <c r="CZ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00982A,00991A,00993A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>台燿科技</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>3.15%</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1.18%</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>1.17%</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="AF13" t="n">
+        <v>431000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>428000</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>-3,000</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="inlineStr"/>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="inlineStr"/>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr"/>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr"/>
+      <c r="CA13" t="inlineStr"/>
+      <c r="CB13" t="inlineStr"/>
+      <c r="CC13" t="inlineStr"/>
+      <c r="CD13" t="inlineStr"/>
+      <c r="CE13" t="inlineStr"/>
+      <c r="CF13" t="inlineStr"/>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="CJ13" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="CK13" t="inlineStr">
+        <is>
+          <t>4.26%</t>
+        </is>
+      </c>
+      <c r="CL13" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="CM13" t="inlineStr">
+        <is>
+          <t>-0.83%</t>
+        </is>
+      </c>
+      <c r="CN13" t="n">
+        <v>306000</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>249000</v>
+      </c>
+      <c r="CP13" t="inlineStr">
+        <is>
+          <t>-57,000</t>
+        </is>
+      </c>
+      <c r="CQ13" t="inlineStr"/>
+      <c r="CR13" t="inlineStr"/>
+      <c r="CS13" t="inlineStr"/>
+      <c r="CT13" t="inlineStr"/>
+      <c r="CU13" t="inlineStr"/>
+      <c r="CV13" t="inlineStr"/>
+      <c r="CW13" t="inlineStr"/>
+      <c r="CX13" t="inlineStr"/>
+      <c r="CY13" t="inlineStr"/>
+      <c r="CZ13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00985A,00991A,00993A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>-0.15%</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>300000</v>
+      </c>
+      <c r="W14" t="n">
+        <v>280000</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>1.74%</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>0.99%</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>-0.75%</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>31000</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>18000</v>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-13,000</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr"/>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr"/>
+      <c r="BW14" t="inlineStr"/>
+      <c r="BX14" t="inlineStr"/>
+      <c r="BY14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr"/>
+      <c r="CA14" t="inlineStr"/>
+      <c r="CB14" t="inlineStr"/>
+      <c r="CC14" t="inlineStr"/>
+      <c r="CD14" t="inlineStr"/>
+      <c r="CE14" t="inlineStr"/>
+      <c r="CF14" t="inlineStr"/>
+      <c r="CG14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI14" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="CJ14" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="CK14" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="CL14" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="CM14" t="inlineStr">
+        <is>
+          <t>-0.75%</t>
+        </is>
+      </c>
+      <c r="CN14" t="n">
+        <v>26000</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>13000</v>
+      </c>
+      <c r="CP14" t="inlineStr">
+        <is>
+          <t>-13,000</t>
+        </is>
+      </c>
+      <c r="CQ14" t="inlineStr"/>
+      <c r="CR14" t="inlineStr"/>
+      <c r="CS14" t="inlineStr"/>
+      <c r="CT14" t="inlineStr"/>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="inlineStr"/>
+      <c r="CW14" t="inlineStr"/>
+      <c r="CX14" t="inlineStr"/>
+      <c r="CY14" t="inlineStr"/>
+      <c r="CZ14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>8299</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>群聯電子</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00985A,00991A,00993A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2.00%</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>-0.26%</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>880000</v>
+      </c>
+      <c r="W15" t="n">
+        <v>780000</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>20000</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>9000</v>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-11,000</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
+      <c r="BQ15" t="inlineStr"/>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr"/>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="inlineStr"/>
+      <c r="CA15" t="inlineStr"/>
+      <c r="CB15" t="inlineStr"/>
+      <c r="CC15" t="inlineStr"/>
+      <c r="CD15" t="inlineStr"/>
+      <c r="CE15" t="inlineStr"/>
+      <c r="CF15" t="inlineStr"/>
+      <c r="CG15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="CJ15" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="CK15" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="CL15" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="CM15" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="CN15" t="n">
+        <v>36000</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>31000</v>
+      </c>
+      <c r="CP15" t="inlineStr">
+        <is>
+          <t>-5,000</t>
+        </is>
+      </c>
+      <c r="CQ15" t="inlineStr"/>
+      <c r="CR15" t="inlineStr"/>
+      <c r="CS15" t="inlineStr"/>
+      <c r="CT15" t="inlineStr"/>
+      <c r="CU15" t="inlineStr"/>
+      <c r="CV15" t="inlineStr"/>
+      <c r="CW15" t="inlineStr"/>
+      <c r="CX15" t="inlineStr"/>
+      <c r="CY15" t="inlineStr"/>
+      <c r="CZ15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>2</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00403A,00993A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>2.00%</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>+0.31%</t>
+        </is>
+      </c>
+      <c r="AP16" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>1,500,000</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr"/>
+      <c r="BQ16" t="inlineStr"/>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr"/>
+      <c r="BW16" t="inlineStr"/>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="inlineStr"/>
+      <c r="CA16" t="inlineStr"/>
+      <c r="CB16" t="inlineStr"/>
+      <c r="CC16" t="inlineStr"/>
+      <c r="CD16" t="inlineStr"/>
+      <c r="CE16" t="inlineStr"/>
+      <c r="CF16" t="inlineStr"/>
+      <c r="CG16" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="CI16" t="inlineStr"/>
+      <c r="CJ16" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="CK16" t="inlineStr"/>
+      <c r="CL16" t="inlineStr">
+        <is>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="CM16" t="inlineStr"/>
+      <c r="CN16" t="inlineStr"/>
+      <c r="CO16" t="n">
+        <v>821000</v>
+      </c>
+      <c r="CP16" t="inlineStr"/>
+      <c r="CQ16" t="inlineStr"/>
+      <c r="CR16" t="inlineStr"/>
+      <c r="CS16" t="inlineStr"/>
+      <c r="CT16" t="inlineStr"/>
+      <c r="CU16" t="inlineStr"/>
+      <c r="CV16" t="inlineStr"/>
+      <c r="CW16" t="inlineStr"/>
+      <c r="CX16" t="inlineStr"/>
+      <c r="CY16" t="inlineStr"/>
+      <c r="CZ16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00982A,00993A</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>4.90%</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
+        <v>184000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>183000</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+      <c r="BO17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr"/>
+      <c r="BQ17" t="inlineStr"/>
+      <c r="BR17" t="inlineStr"/>
+      <c r="BS17" t="inlineStr"/>
+      <c r="BT17" t="inlineStr"/>
+      <c r="BU17" t="inlineStr"/>
+      <c r="BV17" t="inlineStr"/>
+      <c r="BW17" t="inlineStr"/>
+      <c r="BX17" t="inlineStr"/>
+      <c r="BY17" t="inlineStr"/>
+      <c r="BZ17" t="inlineStr"/>
+      <c r="CA17" t="inlineStr"/>
+      <c r="CB17" t="inlineStr"/>
+      <c r="CC17" t="inlineStr"/>
+      <c r="CD17" t="inlineStr"/>
+      <c r="CE17" t="inlineStr"/>
+      <c r="CF17" t="inlineStr"/>
+      <c r="CG17" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI17" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="CJ17" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="CK17" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="CL17" t="inlineStr">
+        <is>
+          <t>4.04%</t>
+        </is>
+      </c>
+      <c r="CM17" t="inlineStr">
+        <is>
+          <t>-0.37%</t>
+        </is>
+      </c>
+      <c r="CN17" t="n">
+        <v>32000</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>30000</v>
+      </c>
+      <c r="CP17" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="CQ17" t="inlineStr"/>
+      <c r="CR17" t="inlineStr"/>
+      <c r="CS17" t="inlineStr"/>
+      <c r="CT17" t="inlineStr"/>
+      <c r="CU17" t="inlineStr"/>
+      <c r="CV17" t="inlineStr"/>
+      <c r="CW17" t="inlineStr"/>
+      <c r="CX17" t="inlineStr"/>
+      <c r="CY17" t="inlineStr"/>
+      <c r="CZ17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00403A,00993A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>15.86%</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>15.59%</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="AP18" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>-300,000</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+      <c r="BO18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr"/>
+      <c r="BQ18" t="inlineStr"/>
+      <c r="BR18" t="inlineStr"/>
+      <c r="BS18" t="inlineStr"/>
+      <c r="BT18" t="inlineStr"/>
+      <c r="BU18" t="inlineStr"/>
+      <c r="BV18" t="inlineStr"/>
+      <c r="BW18" t="inlineStr"/>
+      <c r="BX18" t="inlineStr"/>
+      <c r="BY18" t="inlineStr"/>
+      <c r="BZ18" t="inlineStr"/>
+      <c r="CA18" t="inlineStr"/>
+      <c r="CB18" t="inlineStr"/>
+      <c r="CC18" t="inlineStr"/>
+      <c r="CD18" t="inlineStr"/>
+      <c r="CE18" t="inlineStr"/>
+      <c r="CF18" t="inlineStr"/>
+      <c r="CG18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI18" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="CJ18" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="CK18" t="inlineStr">
+        <is>
+          <t>8.84%</t>
+        </is>
+      </c>
+      <c r="CL18" t="inlineStr">
+        <is>
+          <t>8.39%</t>
+        </is>
+      </c>
+      <c r="CM18" t="inlineStr">
+        <is>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="CN18" t="n">
+        <v>378000</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>363000</v>
+      </c>
+      <c r="CP18" t="inlineStr">
+        <is>
+          <t>-15,000</t>
+        </is>
+      </c>
+      <c r="CQ18" t="inlineStr"/>
+      <c r="CR18" t="inlineStr"/>
+      <c r="CS18" t="inlineStr"/>
+      <c r="CT18" t="inlineStr"/>
+      <c r="CU18" t="inlineStr"/>
+      <c r="CV18" t="inlineStr"/>
+      <c r="CW18" t="inlineStr"/>
+      <c r="CX18" t="inlineStr"/>
+      <c r="CY18" t="inlineStr"/>
+      <c r="CZ18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00403A,00993A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>0.15%</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="AP19" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-1,000,000</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+      <c r="BO19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr"/>
+      <c r="BQ19" t="inlineStr"/>
+      <c r="BR19" t="inlineStr"/>
+      <c r="BS19" t="inlineStr"/>
+      <c r="BT19" t="inlineStr"/>
+      <c r="BU19" t="inlineStr"/>
+      <c r="BV19" t="inlineStr"/>
+      <c r="BW19" t="inlineStr"/>
+      <c r="BX19" t="inlineStr"/>
+      <c r="BY19" t="inlineStr"/>
+      <c r="BZ19" t="inlineStr"/>
+      <c r="CA19" t="inlineStr"/>
+      <c r="CB19" t="inlineStr"/>
+      <c r="CC19" t="inlineStr"/>
+      <c r="CD19" t="inlineStr"/>
+      <c r="CE19" t="inlineStr"/>
+      <c r="CF19" t="inlineStr"/>
+      <c r="CG19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH19" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="CI19" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="CJ19" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="CK19" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="CL19" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="CM19" t="inlineStr">
+        <is>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="CN19" t="n">
+        <v>444000</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>550000</v>
+      </c>
+      <c r="CP19" t="inlineStr">
+        <is>
+          <t>106,000</t>
+        </is>
+      </c>
+      <c r="CQ19" t="inlineStr"/>
+      <c r="CR19" t="inlineStr"/>
+      <c r="CS19" t="inlineStr"/>
+      <c r="CT19" t="inlineStr"/>
+      <c r="CU19" t="inlineStr"/>
+      <c r="CV19" t="inlineStr"/>
+      <c r="CW19" t="inlineStr"/>
+      <c r="CX19" t="inlineStr"/>
+      <c r="CY19" t="inlineStr"/>
+      <c r="CZ19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00403A,00993A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>0.74%</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="AP20" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-2,000,000</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
+      <c r="BO20" t="inlineStr"/>
+      <c r="BP20" t="inlineStr"/>
+      <c r="BQ20" t="inlineStr"/>
+      <c r="BR20" t="inlineStr"/>
+      <c r="BS20" t="inlineStr"/>
+      <c r="BT20" t="inlineStr"/>
+      <c r="BU20" t="inlineStr"/>
+      <c r="BV20" t="inlineStr"/>
+      <c r="BW20" t="inlineStr"/>
+      <c r="BX20" t="inlineStr"/>
+      <c r="BY20" t="inlineStr"/>
+      <c r="BZ20" t="inlineStr"/>
+      <c r="CA20" t="inlineStr"/>
+      <c r="CB20" t="inlineStr"/>
+      <c r="CC20" t="inlineStr"/>
+      <c r="CD20" t="inlineStr"/>
+      <c r="CE20" t="inlineStr"/>
+      <c r="CF20" t="inlineStr"/>
+      <c r="CG20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI20" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="CJ20" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="CK20" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
+      <c r="CL20" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="CM20" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="CN20" t="n">
+        <v>1610000</v>
+      </c>
+      <c r="CO20" t="n">
+        <v>1496000</v>
+      </c>
+      <c r="CP20" t="inlineStr">
+        <is>
+          <t>-114,000</t>
+        </is>
+      </c>
+      <c r="CQ20" t="inlineStr"/>
+      <c r="CR20" t="inlineStr"/>
+      <c r="CS20" t="inlineStr"/>
+      <c r="CT20" t="inlineStr"/>
+      <c r="CU20" t="inlineStr"/>
+      <c r="CV20" t="inlineStr"/>
+      <c r="CW20" t="inlineStr"/>
+      <c r="CX20" t="inlineStr"/>
+      <c r="CY20" t="inlineStr"/>
+      <c r="CZ20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00407A,00993A</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+      <c r="BO21" t="inlineStr"/>
+      <c r="BP21" t="inlineStr"/>
+      <c r="BQ21" t="inlineStr"/>
+      <c r="BR21" t="inlineStr"/>
+      <c r="BS21" t="inlineStr"/>
+      <c r="BT21" t="inlineStr"/>
+      <c r="BU21" t="inlineStr"/>
+      <c r="BV21" t="inlineStr"/>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>2.12%</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>1.16%</t>
+        </is>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>-0.96%</t>
+        </is>
+      </c>
+      <c r="CD21" t="n">
+        <v>1025000</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>595000</v>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>-430,000</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI21" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="CJ21" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="CK21" t="inlineStr">
+        <is>
+          <t>4.10%</t>
+        </is>
+      </c>
+      <c r="CL21" t="inlineStr">
+        <is>
+          <t>3.76%</t>
+        </is>
+      </c>
+      <c r="CM21" t="inlineStr">
+        <is>
+          <t>-0.34%</t>
+        </is>
+      </c>
+      <c r="CN21" t="n">
+        <v>778000</v>
+      </c>
+      <c r="CO21" t="n">
+        <v>763000</v>
+      </c>
+      <c r="CP21" t="inlineStr">
+        <is>
+          <t>-15,000</t>
+        </is>
+      </c>
+      <c r="CQ21" t="inlineStr"/>
+      <c r="CR21" t="inlineStr"/>
+      <c r="CS21" t="inlineStr"/>
+      <c r="CT21" t="inlineStr"/>
+      <c r="CU21" t="inlineStr"/>
+      <c r="CV21" t="inlineStr"/>
+      <c r="CW21" t="inlineStr"/>
+      <c r="CX21" t="inlineStr"/>
+      <c r="CY21" t="inlineStr"/>
+      <c r="CZ21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>文曄科技</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>00985A,00993A</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="AT22" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>文曄科技</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>文曄科技</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>-0.84%</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>475000</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>27000</v>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-448,000</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+      <c r="BO22" t="inlineStr"/>
+      <c r="BP22" t="inlineStr"/>
+      <c r="BQ22" t="inlineStr"/>
+      <c r="BR22" t="inlineStr"/>
+      <c r="BS22" t="inlineStr"/>
+      <c r="BT22" t="inlineStr"/>
+      <c r="BU22" t="inlineStr"/>
+      <c r="BV22" t="inlineStr"/>
+      <c r="BW22" t="inlineStr"/>
+      <c r="BX22" t="inlineStr"/>
+      <c r="BY22" t="inlineStr"/>
+      <c r="BZ22" t="inlineStr"/>
+      <c r="CA22" t="inlineStr"/>
+      <c r="CB22" t="inlineStr"/>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="CH22" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr">
+        <is>
+          <t>文曄</t>
+        </is>
+      </c>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="CM22" t="inlineStr"/>
+      <c r="CN22" t="inlineStr"/>
+      <c r="CO22" t="n">
+        <v>149000</v>
+      </c>
+      <c r="CP22" t="inlineStr"/>
+      <c r="CQ22" t="inlineStr"/>
+      <c r="CR22" t="inlineStr"/>
+      <c r="CS22" t="inlineStr"/>
+      <c r="CT22" t="inlineStr"/>
+      <c r="CU22" t="inlineStr"/>
+      <c r="CV22" t="inlineStr"/>
+      <c r="CW22" t="inlineStr"/>
+      <c r="CX22" t="inlineStr"/>
+      <c r="CY22" t="inlineStr"/>
+      <c r="CZ22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>欣興電子</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>欣興電子</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>欣興電子</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>1.94%</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>2.30%</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>+0.36%</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>202000</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>252000</v>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+      <c r="BO23" t="inlineStr"/>
+      <c r="BP23" t="inlineStr"/>
+      <c r="BQ23" t="inlineStr"/>
+      <c r="BR23" t="inlineStr"/>
+      <c r="BS23" t="inlineStr"/>
+      <c r="BT23" t="inlineStr"/>
+      <c r="BU23" t="inlineStr"/>
+      <c r="BV23" t="inlineStr"/>
+      <c r="BW23" t="inlineStr"/>
+      <c r="BX23" t="inlineStr"/>
+      <c r="BY23" t="inlineStr"/>
+      <c r="BZ23" t="inlineStr"/>
+      <c r="CA23" t="inlineStr"/>
+      <c r="CB23" t="inlineStr"/>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI23" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="CJ23" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="CK23" t="inlineStr">
+        <is>
+          <t>5.46%</t>
+        </is>
+      </c>
+      <c r="CL23" t="inlineStr">
+        <is>
+          <t>4.19%</t>
+        </is>
+      </c>
+      <c r="CM23" t="inlineStr">
+        <is>
+          <t>-1.27%</t>
+        </is>
+      </c>
+      <c r="CN23" t="n">
+        <v>563000</v>
+      </c>
+      <c r="CO23" t="n">
+        <v>454000</v>
+      </c>
+      <c r="CP23" t="inlineStr">
+        <is>
+          <t>-109,000</t>
+        </is>
+      </c>
+      <c r="CQ23" t="inlineStr"/>
+      <c r="CR23" t="inlineStr"/>
+      <c r="CS23" t="inlineStr"/>
+      <c r="CT23" t="inlineStr"/>
+      <c r="CU23" t="inlineStr"/>
+      <c r="CV23" t="inlineStr"/>
+      <c r="CW23" t="inlineStr"/>
+      <c r="CX23" t="inlineStr"/>
+      <c r="CY23" t="inlineStr"/>
+      <c r="CZ23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>00982A,00993A</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1.17%</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="AF24" t="n">
+        <v>3405000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3404000</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
+      <c r="BO24" t="inlineStr"/>
+      <c r="BP24" t="inlineStr"/>
+      <c r="BQ24" t="inlineStr"/>
+      <c r="BR24" t="inlineStr"/>
+      <c r="BS24" t="inlineStr"/>
+      <c r="BT24" t="inlineStr"/>
+      <c r="BU24" t="inlineStr"/>
+      <c r="BV24" t="inlineStr"/>
+      <c r="BW24" t="inlineStr"/>
+      <c r="BX24" t="inlineStr"/>
+      <c r="BY24" t="inlineStr"/>
+      <c r="BZ24" t="inlineStr"/>
+      <c r="CA24" t="inlineStr"/>
+      <c r="CB24" t="inlineStr"/>
+      <c r="CC24" t="inlineStr"/>
+      <c r="CD24" t="inlineStr"/>
+      <c r="CE24" t="inlineStr"/>
+      <c r="CF24" t="inlineStr"/>
+      <c r="CG24" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH24" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="CI24" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="CJ24" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="CK24" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="CL24" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+      <c r="CM24" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
+        </is>
+      </c>
+      <c r="CN24" t="n">
+        <v>260000</v>
+      </c>
+      <c r="CO24" t="n">
+        <v>611000</v>
+      </c>
+      <c r="CP24" t="inlineStr">
+        <is>
+          <t>351,000</t>
+        </is>
+      </c>
+      <c r="CQ24" t="inlineStr"/>
+      <c r="CR24" t="inlineStr"/>
+      <c r="CS24" t="inlineStr"/>
+      <c r="CT24" t="inlineStr"/>
+      <c r="CU24" t="inlineStr"/>
+      <c r="CV24" t="inlineStr"/>
+      <c r="CW24" t="inlineStr"/>
+      <c r="CX24" t="inlineStr"/>
+      <c r="CY24" t="inlineStr"/>
+      <c r="CZ24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>0.42%</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0.18%</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>-0.24%</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M13" t="n">
-        <v>9000</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-11,000</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>5916000</v>
+      </c>
+      <c r="M25" t="n">
+        <v>5028000</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-888,000</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
+      <c r="BO25" t="inlineStr"/>
+      <c r="BP25" t="inlineStr"/>
+      <c r="BQ25" t="inlineStr"/>
+      <c r="BR25" t="inlineStr"/>
+      <c r="BS25" t="inlineStr"/>
+      <c r="BT25" t="inlineStr"/>
+      <c r="BU25" t="inlineStr"/>
+      <c r="BV25" t="inlineStr"/>
+      <c r="BW25" t="inlineStr"/>
+      <c r="BX25" t="inlineStr"/>
+      <c r="BY25" t="inlineStr"/>
+      <c r="BZ25" t="inlineStr"/>
+      <c r="CA25" t="inlineStr"/>
+      <c r="CB25" t="inlineStr"/>
+      <c r="CC25" t="inlineStr"/>
+      <c r="CD25" t="inlineStr"/>
+      <c r="CE25" t="inlineStr"/>
+      <c r="CF25" t="inlineStr"/>
+      <c r="CG25" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="CH25" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="CI25" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="CJ25" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="CK25" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="CL25" t="inlineStr">
+        <is>
+          <t>0.83%</t>
+        </is>
+      </c>
+      <c r="CM25" t="inlineStr">
+        <is>
+          <t>+0.40%</t>
+        </is>
+      </c>
+      <c r="CN25" t="n">
+        <v>195000</v>
+      </c>
+      <c r="CO25" t="n">
+        <v>367000</v>
+      </c>
+      <c r="CP25" t="inlineStr">
+        <is>
+          <t>172,000</t>
+        </is>
+      </c>
+      <c r="CQ25" t="inlineStr"/>
+      <c r="CR25" t="inlineStr"/>
+      <c r="CS25" t="inlineStr"/>
+      <c r="CT25" t="inlineStr"/>
+      <c r="CU25" t="inlineStr"/>
+      <c r="CV25" t="inlineStr"/>
+      <c r="CW25" t="inlineStr"/>
+      <c r="CX25" t="inlineStr"/>
+      <c r="CY25" t="inlineStr"/>
+      <c r="CZ25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00405A,00993A</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN26" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>0.76%</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>0.63%</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>-0.13%</t>
-        </is>
-      </c>
-      <c r="AF13" t="n">
+      <c r="BO26" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="BP26" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="BQ26" t="inlineStr">
+        <is>
+          <t>7.48%</t>
+        </is>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>6.37%</t>
+        </is>
+      </c>
+      <c r="BS26" t="inlineStr">
+        <is>
+          <t>-1.11%</t>
+        </is>
+      </c>
+      <c r="BT26" t="n">
+        <v>370000</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>310000</v>
+      </c>
+      <c r="BV26" t="inlineStr">
+        <is>
+          <t>-60,000</t>
+        </is>
+      </c>
+      <c r="BW26" t="inlineStr"/>
+      <c r="BX26" t="inlineStr"/>
+      <c r="BY26" t="inlineStr"/>
+      <c r="BZ26" t="inlineStr"/>
+      <c r="CA26" t="inlineStr"/>
+      <c r="CB26" t="inlineStr"/>
+      <c r="CC26" t="inlineStr"/>
+      <c r="CD26" t="inlineStr"/>
+      <c r="CE26" t="inlineStr"/>
+      <c r="CF26" t="inlineStr"/>
+      <c r="CG26" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH26" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI26" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="CJ26" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="CK26" t="inlineStr">
+        <is>
+          <t>2.09%</t>
+        </is>
+      </c>
+      <c r="CL26" t="inlineStr">
+        <is>
+          <t>1.62%</t>
+        </is>
+      </c>
+      <c r="CM26" t="inlineStr">
+        <is>
+          <t>-0.47%</t>
+        </is>
+      </c>
+      <c r="CN26" t="n">
         <v>36000</v>
       </c>
-      <c r="AG13" t="n">
-        <v>31000</v>
-      </c>
-      <c r="AH13" t="inlineStr">
+      <c r="CO26" t="n">
+        <v>29000</v>
+      </c>
+      <c r="CP26" t="inlineStr">
+        <is>
+          <t>-7,000</t>
+        </is>
+      </c>
+      <c r="CQ26" t="inlineStr"/>
+      <c r="CR26" t="inlineStr"/>
+      <c r="CS26" t="inlineStr"/>
+      <c r="CT26" t="inlineStr"/>
+      <c r="CU26" t="inlineStr"/>
+      <c r="CV26" t="inlineStr"/>
+      <c r="CW26" t="inlineStr"/>
+      <c r="CX26" t="inlineStr"/>
+      <c r="CY26" t="inlineStr"/>
+      <c r="CZ26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>貿聯控股（BizLink Holding In</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>貿聯控股（BizLink Holding In</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>貿聯控股（BizLink Holding In</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>2.29%</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>+0.31%</t>
+        </is>
+      </c>
+      <c r="AZ27" t="n">
+        <v>95000</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>105000</v>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="inlineStr"/>
+      <c r="BO27" t="inlineStr"/>
+      <c r="BP27" t="inlineStr"/>
+      <c r="BQ27" t="inlineStr"/>
+      <c r="BR27" t="inlineStr"/>
+      <c r="BS27" t="inlineStr"/>
+      <c r="BT27" t="inlineStr"/>
+      <c r="BU27" t="inlineStr"/>
+      <c r="BV27" t="inlineStr"/>
+      <c r="BW27" t="inlineStr"/>
+      <c r="BX27" t="inlineStr"/>
+      <c r="BY27" t="inlineStr"/>
+      <c r="BZ27" t="inlineStr"/>
+      <c r="CA27" t="inlineStr"/>
+      <c r="CB27" t="inlineStr"/>
+      <c r="CC27" t="inlineStr"/>
+      <c r="CD27" t="inlineStr"/>
+      <c r="CE27" t="inlineStr"/>
+      <c r="CF27" t="inlineStr"/>
+      <c r="CG27" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH27" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="CI27" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="CJ27" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="CK27" t="inlineStr">
+        <is>
+          <t>1.85%</t>
+        </is>
+      </c>
+      <c r="CL27" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="CM27" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
+      <c r="CN27" t="n">
+        <v>88000</v>
+      </c>
+      <c r="CO27" t="n">
+        <v>90000</v>
+      </c>
+      <c r="CP27" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="CQ27" t="inlineStr"/>
+      <c r="CR27" t="inlineStr"/>
+      <c r="CS27" t="inlineStr"/>
+      <c r="CT27" t="inlineStr"/>
+      <c r="CU27" t="inlineStr"/>
+      <c r="CV27" t="inlineStr"/>
+      <c r="CW27" t="inlineStr"/>
+      <c r="CX27" t="inlineStr"/>
+      <c r="CY27" t="inlineStr"/>
+      <c r="CZ27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00982A,00993A</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>3.09%</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>3178000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3158000</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="inlineStr"/>
+      <c r="BO28" t="inlineStr"/>
+      <c r="BP28" t="inlineStr"/>
+      <c r="BQ28" t="inlineStr"/>
+      <c r="BR28" t="inlineStr"/>
+      <c r="BS28" t="inlineStr"/>
+      <c r="BT28" t="inlineStr"/>
+      <c r="BU28" t="inlineStr"/>
+      <c r="BV28" t="inlineStr"/>
+      <c r="BW28" t="inlineStr"/>
+      <c r="BX28" t="inlineStr"/>
+      <c r="BY28" t="inlineStr"/>
+      <c r="BZ28" t="inlineStr"/>
+      <c r="CA28" t="inlineStr"/>
+      <c r="CB28" t="inlineStr"/>
+      <c r="CC28" t="inlineStr"/>
+      <c r="CD28" t="inlineStr"/>
+      <c r="CE28" t="inlineStr"/>
+      <c r="CF28" t="inlineStr"/>
+      <c r="CG28" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="CH28" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="CI28" t="inlineStr"/>
+      <c r="CJ28" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="CK28" t="inlineStr"/>
+      <c r="CL28" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="CM28" t="inlineStr"/>
+      <c r="CN28" t="inlineStr"/>
+      <c r="CO28" t="n">
+        <v>171000</v>
+      </c>
+      <c r="CP28" t="inlineStr"/>
+      <c r="CQ28" t="inlineStr"/>
+      <c r="CR28" t="inlineStr"/>
+      <c r="CS28" t="inlineStr"/>
+      <c r="CT28" t="inlineStr"/>
+      <c r="CU28" t="inlineStr"/>
+      <c r="CV28" t="inlineStr"/>
+      <c r="CW28" t="inlineStr"/>
+      <c r="CX28" t="inlineStr"/>
+      <c r="CY28" t="inlineStr"/>
+      <c r="CZ28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>00982A,00993A</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>5.52%</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>5.26%</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>-0.26%</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3771000</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>-29,000</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr"/>
+      <c r="BJ29" t="inlineStr"/>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="inlineStr"/>
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="inlineStr"/>
+      <c r="BO29" t="inlineStr"/>
+      <c r="BP29" t="inlineStr"/>
+      <c r="BQ29" t="inlineStr"/>
+      <c r="BR29" t="inlineStr"/>
+      <c r="BS29" t="inlineStr"/>
+      <c r="BT29" t="inlineStr"/>
+      <c r="BU29" t="inlineStr"/>
+      <c r="BV29" t="inlineStr"/>
+      <c r="BW29" t="inlineStr"/>
+      <c r="BX29" t="inlineStr"/>
+      <c r="BY29" t="inlineStr"/>
+      <c r="BZ29" t="inlineStr"/>
+      <c r="CA29" t="inlineStr"/>
+      <c r="CB29" t="inlineStr"/>
+      <c r="CC29" t="inlineStr"/>
+      <c r="CD29" t="inlineStr"/>
+      <c r="CE29" t="inlineStr"/>
+      <c r="CF29" t="inlineStr"/>
+      <c r="CG29" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH29" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="CI29" t="inlineStr">
+        <is>
+          <t>亞翔工程</t>
+        </is>
+      </c>
+      <c r="CJ29" t="inlineStr">
+        <is>
+          <t>亞翔工程</t>
+        </is>
+      </c>
+      <c r="CK29" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="CL29" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="CM29" t="inlineStr">
+        <is>
+          <t>+0.40%</t>
+        </is>
+      </c>
+      <c r="CN29" t="n">
+        <v>48000</v>
+      </c>
+      <c r="CO29" t="n">
+        <v>102000</v>
+      </c>
+      <c r="CP29" t="inlineStr">
+        <is>
+          <t>54,000</t>
+        </is>
+      </c>
+      <c r="CQ29" t="inlineStr"/>
+      <c r="CR29" t="inlineStr"/>
+      <c r="CS29" t="inlineStr"/>
+      <c r="CT29" t="inlineStr"/>
+      <c r="CU29" t="inlineStr"/>
+      <c r="CV29" t="inlineStr"/>
+      <c r="CW29" t="inlineStr"/>
+      <c r="CX29" t="inlineStr"/>
+      <c r="CY29" t="inlineStr"/>
+      <c r="CZ29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>-7,000</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
+      <c r="BH30" t="inlineStr"/>
+      <c r="BI30" t="inlineStr"/>
+      <c r="BJ30" t="inlineStr"/>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="inlineStr"/>
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="inlineStr"/>
+      <c r="BO30" t="inlineStr"/>
+      <c r="BP30" t="inlineStr"/>
+      <c r="BQ30" t="inlineStr"/>
+      <c r="BR30" t="inlineStr"/>
+      <c r="BS30" t="inlineStr"/>
+      <c r="BT30" t="inlineStr"/>
+      <c r="BU30" t="inlineStr"/>
+      <c r="BV30" t="inlineStr"/>
+      <c r="BW30" t="inlineStr"/>
+      <c r="BX30" t="inlineStr"/>
+      <c r="BY30" t="inlineStr"/>
+      <c r="BZ30" t="inlineStr"/>
+      <c r="CA30" t="inlineStr"/>
+      <c r="CB30" t="inlineStr"/>
+      <c r="CC30" t="inlineStr"/>
+      <c r="CD30" t="inlineStr"/>
+      <c r="CE30" t="inlineStr"/>
+      <c r="CF30" t="inlineStr"/>
+      <c r="CG30" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH30" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI30" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="CJ30" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="CK30" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="CL30" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="CM30" t="inlineStr">
+        <is>
+          <t>-0.25%</t>
+        </is>
+      </c>
+      <c r="CN30" t="n">
+        <v>38000</v>
+      </c>
+      <c r="CO30" t="n">
+        <v>19000</v>
+      </c>
+      <c r="CP30" t="inlineStr">
+        <is>
+          <t>-19,000</t>
+        </is>
+      </c>
+      <c r="CQ30" t="inlineStr"/>
+      <c r="CR30" t="inlineStr"/>
+      <c r="CS30" t="inlineStr"/>
+      <c r="CT30" t="inlineStr"/>
+      <c r="CU30" t="inlineStr"/>
+      <c r="CV30" t="inlineStr"/>
+      <c r="CW30" t="inlineStr"/>
+      <c r="CX30" t="inlineStr"/>
+      <c r="CY30" t="inlineStr"/>
+      <c r="CZ30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>00982A,00993A</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="AF31" t="n">
+        <v>307000</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>305000</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr"/>
+      <c r="BJ31" t="inlineStr"/>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="inlineStr"/>
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="inlineStr"/>
+      <c r="BO31" t="inlineStr"/>
+      <c r="BP31" t="inlineStr"/>
+      <c r="BQ31" t="inlineStr"/>
+      <c r="BR31" t="inlineStr"/>
+      <c r="BS31" t="inlineStr"/>
+      <c r="BT31" t="inlineStr"/>
+      <c r="BU31" t="inlineStr"/>
+      <c r="BV31" t="inlineStr"/>
+      <c r="BW31" t="inlineStr"/>
+      <c r="BX31" t="inlineStr"/>
+      <c r="BY31" t="inlineStr"/>
+      <c r="BZ31" t="inlineStr"/>
+      <c r="CA31" t="inlineStr"/>
+      <c r="CB31" t="inlineStr"/>
+      <c r="CC31" t="inlineStr"/>
+      <c r="CD31" t="inlineStr"/>
+      <c r="CE31" t="inlineStr"/>
+      <c r="CF31" t="inlineStr"/>
+      <c r="CG31" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH31" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI31" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="CJ31" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="CK31" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="CL31" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="CM31" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="CN31" t="n">
+        <v>79000</v>
+      </c>
+      <c r="CO31" t="n">
+        <v>39000</v>
+      </c>
+      <c r="CP31" t="inlineStr">
+        <is>
+          <t>-40,000</t>
+        </is>
+      </c>
+      <c r="CQ31" t="inlineStr"/>
+      <c r="CR31" t="inlineStr"/>
+      <c r="CS31" t="inlineStr"/>
+      <c r="CT31" t="inlineStr"/>
+      <c r="CU31" t="inlineStr"/>
+      <c r="CV31" t="inlineStr"/>
+      <c r="CW31" t="inlineStr"/>
+      <c r="CX31" t="inlineStr"/>
+      <c r="CY31" t="inlineStr"/>
+      <c r="CZ31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>00982A,00985A</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2.08%</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>2.06%</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="AF32" t="n">
+        <v>1108000</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>環球晶圓</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>環球晶圓</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>0.09%</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>+1.54%</t>
+        </is>
+      </c>
+      <c r="AZ32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>174000</v>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>164,000</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
+      <c r="BH32" t="inlineStr"/>
+      <c r="BI32" t="inlineStr"/>
+      <c r="BJ32" t="inlineStr"/>
+      <c r="BK32" t="inlineStr"/>
+      <c r="BL32" t="inlineStr"/>
+      <c r="BM32" t="inlineStr"/>
+      <c r="BN32" t="inlineStr"/>
+      <c r="BO32" t="inlineStr"/>
+      <c r="BP32" t="inlineStr"/>
+      <c r="BQ32" t="inlineStr"/>
+      <c r="BR32" t="inlineStr"/>
+      <c r="BS32" t="inlineStr"/>
+      <c r="BT32" t="inlineStr"/>
+      <c r="BU32" t="inlineStr"/>
+      <c r="BV32" t="inlineStr"/>
+      <c r="BW32" t="inlineStr"/>
+      <c r="BX32" t="inlineStr"/>
+      <c r="BY32" t="inlineStr"/>
+      <c r="BZ32" t="inlineStr"/>
+      <c r="CA32" t="inlineStr"/>
+      <c r="CB32" t="inlineStr"/>
+      <c r="CC32" t="inlineStr"/>
+      <c r="CD32" t="inlineStr"/>
+      <c r="CE32" t="inlineStr"/>
+      <c r="CF32" t="inlineStr"/>
+      <c r="CG32" t="inlineStr"/>
+      <c r="CH32" t="inlineStr"/>
+      <c r="CI32" t="inlineStr"/>
+      <c r="CJ32" t="inlineStr"/>
+      <c r="CK32" t="inlineStr"/>
+      <c r="CL32" t="inlineStr"/>
+      <c r="CM32" t="inlineStr"/>
+      <c r="CN32" t="inlineStr"/>
+      <c r="CO32" t="inlineStr"/>
+      <c r="CP32" t="inlineStr"/>
+      <c r="CQ32" t="inlineStr"/>
+      <c r="CR32" t="inlineStr"/>
+      <c r="CS32" t="inlineStr"/>
+      <c r="CT32" t="inlineStr"/>
+      <c r="CU32" t="inlineStr"/>
+      <c r="CV32" t="inlineStr"/>
+      <c r="CW32" t="inlineStr"/>
+      <c r="CX32" t="inlineStr"/>
+      <c r="CY32" t="inlineStr"/>
+      <c r="CZ32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>00407A,00981A</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>477000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>561000</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>84,000</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
+      <c r="BI33" t="inlineStr"/>
+      <c r="BJ33" t="inlineStr"/>
+      <c r="BK33" t="inlineStr"/>
+      <c r="BL33" t="inlineStr"/>
+      <c r="BM33" t="inlineStr"/>
+      <c r="BN33" t="inlineStr"/>
+      <c r="BO33" t="inlineStr"/>
+      <c r="BP33" t="inlineStr"/>
+      <c r="BQ33" t="inlineStr"/>
+      <c r="BR33" t="inlineStr"/>
+      <c r="BS33" t="inlineStr"/>
+      <c r="BT33" t="inlineStr"/>
+      <c r="BU33" t="inlineStr"/>
+      <c r="BV33" t="inlineStr"/>
+      <c r="BW33" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="BX33" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="BY33" t="inlineStr"/>
+      <c r="BZ33" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="CA33" t="inlineStr"/>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="CC33" t="inlineStr"/>
+      <c r="CD33" t="inlineStr"/>
+      <c r="CE33" t="n">
+        <v>2000</v>
+      </c>
+      <c r="CF33" t="inlineStr"/>
+      <c r="CG33" t="inlineStr"/>
+      <c r="CH33" t="inlineStr"/>
+      <c r="CI33" t="inlineStr"/>
+      <c r="CJ33" t="inlineStr"/>
+      <c r="CK33" t="inlineStr"/>
+      <c r="CL33" t="inlineStr"/>
+      <c r="CM33" t="inlineStr"/>
+      <c r="CN33" t="inlineStr"/>
+      <c r="CO33" t="inlineStr"/>
+      <c r="CP33" t="inlineStr"/>
+      <c r="CQ33" t="inlineStr"/>
+      <c r="CR33" t="inlineStr"/>
+      <c r="CS33" t="inlineStr"/>
+      <c r="CT33" t="inlineStr"/>
+      <c r="CU33" t="inlineStr"/>
+      <c r="CV33" t="inlineStr"/>
+      <c r="CW33" t="inlineStr"/>
+      <c r="CX33" t="inlineStr"/>
+      <c r="CY33" t="inlineStr"/>
+      <c r="CZ33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>00407A,00993A</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="inlineStr"/>
+      <c r="BJ34" t="inlineStr"/>
+      <c r="BK34" t="inlineStr"/>
+      <c r="BL34" t="inlineStr"/>
+      <c r="BM34" t="inlineStr"/>
+      <c r="BN34" t="inlineStr"/>
+      <c r="BO34" t="inlineStr"/>
+      <c r="BP34" t="inlineStr"/>
+      <c r="BQ34" t="inlineStr"/>
+      <c r="BR34" t="inlineStr"/>
+      <c r="BS34" t="inlineStr"/>
+      <c r="BT34" t="inlineStr"/>
+      <c r="BU34" t="inlineStr"/>
+      <c r="BV34" t="inlineStr"/>
+      <c r="BW34" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="BX34" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="BY34" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="BZ34" t="inlineStr"/>
+      <c r="CA34" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="CB34" t="inlineStr"/>
+      <c r="CC34" t="inlineStr"/>
+      <c r="CD34" t="n">
+        <v>8000</v>
+      </c>
+      <c r="CE34" t="inlineStr"/>
+      <c r="CF34" t="inlineStr"/>
+      <c r="CG34" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH34" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="CI34" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="CJ34" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="CK34" t="inlineStr">
+        <is>
+          <t>2.38%</t>
+        </is>
+      </c>
+      <c r="CL34" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="CM34" t="inlineStr">
+        <is>
+          <t>-0.15%</t>
+        </is>
+      </c>
+      <c r="CN34" t="n">
+        <v>39000</v>
+      </c>
+      <c r="CO34" t="n">
+        <v>34000</v>
+      </c>
+      <c r="CP34" t="inlineStr">
         <is>
           <t>-5,000</t>
         </is>
       </c>
+      <c r="CQ34" t="inlineStr"/>
+      <c r="CR34" t="inlineStr"/>
+      <c r="CS34" t="inlineStr"/>
+      <c r="CT34" t="inlineStr"/>
+      <c r="CU34" t="inlineStr"/>
+      <c r="CV34" t="inlineStr"/>
+      <c r="CW34" t="inlineStr"/>
+      <c r="CX34" t="inlineStr"/>
+      <c r="CY34" t="inlineStr"/>
+      <c r="CZ34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>00403A,00993A</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>1.44%</t>
+        </is>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>1.12%</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="AP35" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>850000</v>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr"/>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
+      <c r="BH35" t="inlineStr"/>
+      <c r="BI35" t="inlineStr"/>
+      <c r="BJ35" t="inlineStr"/>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
+      <c r="BN35" t="inlineStr"/>
+      <c r="BO35" t="inlineStr"/>
+      <c r="BP35" t="inlineStr"/>
+      <c r="BQ35" t="inlineStr"/>
+      <c r="BR35" t="inlineStr"/>
+      <c r="BS35" t="inlineStr"/>
+      <c r="BT35" t="inlineStr"/>
+      <c r="BU35" t="inlineStr"/>
+      <c r="BV35" t="inlineStr"/>
+      <c r="BW35" t="inlineStr"/>
+      <c r="BX35" t="inlineStr"/>
+      <c r="BY35" t="inlineStr"/>
+      <c r="BZ35" t="inlineStr"/>
+      <c r="CA35" t="inlineStr"/>
+      <c r="CB35" t="inlineStr"/>
+      <c r="CC35" t="inlineStr"/>
+      <c r="CD35" t="inlineStr"/>
+      <c r="CE35" t="inlineStr"/>
+      <c r="CF35" t="inlineStr"/>
+      <c r="CG35" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="CH35" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="CI35" t="inlineStr"/>
+      <c r="CJ35" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="CK35" t="inlineStr"/>
+      <c r="CL35" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="CM35" t="inlineStr"/>
+      <c r="CN35" t="inlineStr"/>
+      <c r="CO35" t="n">
+        <v>36000</v>
+      </c>
+      <c r="CP35" t="inlineStr"/>
+      <c r="CQ35" t="inlineStr"/>
+      <c r="CR35" t="inlineStr"/>
+      <c r="CS35" t="inlineStr"/>
+      <c r="CT35" t="inlineStr"/>
+      <c r="CU35" t="inlineStr"/>
+      <c r="CV35" t="inlineStr"/>
+      <c r="CW35" t="inlineStr"/>
+      <c r="CX35" t="inlineStr"/>
+      <c r="CY35" t="inlineStr"/>
+      <c r="CZ35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>金居</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>00403A,00993A</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>金居</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>金居</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>0.13%</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="AP36" t="n">
+        <v>600000</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr"/>
+      <c r="BJ36" t="inlineStr"/>
+      <c r="BK36" t="inlineStr"/>
+      <c r="BL36" t="inlineStr"/>
+      <c r="BM36" t="inlineStr"/>
+      <c r="BN36" t="inlineStr"/>
+      <c r="BO36" t="inlineStr"/>
+      <c r="BP36" t="inlineStr"/>
+      <c r="BQ36" t="inlineStr"/>
+      <c r="BR36" t="inlineStr"/>
+      <c r="BS36" t="inlineStr"/>
+      <c r="BT36" t="inlineStr"/>
+      <c r="BU36" t="inlineStr"/>
+      <c r="BV36" t="inlineStr"/>
+      <c r="BW36" t="inlineStr"/>
+      <c r="BX36" t="inlineStr"/>
+      <c r="BY36" t="inlineStr"/>
+      <c r="BZ36" t="inlineStr"/>
+      <c r="CA36" t="inlineStr"/>
+      <c r="CB36" t="inlineStr"/>
+      <c r="CC36" t="inlineStr"/>
+      <c r="CD36" t="inlineStr"/>
+      <c r="CE36" t="inlineStr"/>
+      <c r="CF36" t="inlineStr"/>
+      <c r="CG36" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="CH36" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="CI36" t="inlineStr">
+        <is>
+          <t>金居開發</t>
+        </is>
+      </c>
+      <c r="CJ36" t="inlineStr">
+        <is>
+          <t>金居開發</t>
+        </is>
+      </c>
+      <c r="CK36" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="CL36" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="CM36" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="CN36" t="n">
+        <v>87000</v>
+      </c>
+      <c r="CO36" t="n">
+        <v>108000</v>
+      </c>
+      <c r="CP36" t="inlineStr">
+        <is>
+          <t>21,000</t>
+        </is>
+      </c>
+      <c r="CQ36" t="inlineStr"/>
+      <c r="CR36" t="inlineStr"/>
+      <c r="CS36" t="inlineStr"/>
+      <c r="CT36" t="inlineStr"/>
+      <c r="CU36" t="inlineStr"/>
+      <c r="CV36" t="inlineStr"/>
+      <c r="CW36" t="inlineStr"/>
+      <c r="CX36" t="inlineStr"/>
+      <c r="CY36" t="inlineStr"/>
+      <c r="CZ36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
